--- a/Dataset_interaction.xlsx
+++ b/Dataset_interaction.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1ede7f09fdbafa1e/R Analysis/RSGI mBC Subtype Modeling/Manuscript Trend/github/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walid/Desktop/Trend_github/TREND_MBC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{02C5DED7-9D48-5D40-A091-9EDB0710D46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{315620CC-ECBC-3E4D-A494-8CCAC77E14CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C4853E-F3C8-FD4B-9E60-63CD75039F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,49 +50,49 @@
     <t>Combination</t>
   </si>
   <si>
+    <t>DTX + DOX</t>
+  </si>
+  <si>
+    <t>DOX + GEM</t>
+  </si>
+  <si>
+    <t>Lapatinib + Vino</t>
+  </si>
+  <si>
+    <t>Cisplatin + Vino</t>
+  </si>
+  <si>
+    <t>DTX + Vino</t>
+  </si>
+  <si>
+    <t>Bevacizu + DTX</t>
+  </si>
+  <si>
+    <t>Carbo + DTX</t>
+  </si>
+  <si>
+    <t>Antagonistic</t>
+  </si>
+  <si>
+    <t>Synergistic</t>
+  </si>
+  <si>
+    <t>DTX + GEM</t>
+  </si>
+  <si>
+    <t>DOX + PTX</t>
+  </si>
+  <si>
+    <t>Cape + Vino</t>
+  </si>
+  <si>
+    <t>CTX + Epirubicin</t>
+  </si>
+  <si>
+    <t>CTX + DTX + DOX</t>
+  </si>
+  <si>
     <t>Interaction</t>
-  </si>
-  <si>
-    <t>DTX + DOX</t>
-  </si>
-  <si>
-    <t>DOX + GEM</t>
-  </si>
-  <si>
-    <t>Lapatinib + Vino</t>
-  </si>
-  <si>
-    <t>Cisplatin + Vino</t>
-  </si>
-  <si>
-    <t>DTX + Vino</t>
-  </si>
-  <si>
-    <t>Bevacizu + DTX</t>
-  </si>
-  <si>
-    <t>Carbo + DTX</t>
-  </si>
-  <si>
-    <t>DOX + PTX + Trastuzu</t>
-  </si>
-  <si>
-    <t>Antagonistic</t>
-  </si>
-  <si>
-    <t>Synergistic</t>
-  </si>
-  <si>
-    <t>DTX + GEM</t>
-  </si>
-  <si>
-    <t>DOX + PTX</t>
-  </si>
-  <si>
-    <t>Cape + Vino</t>
-  </si>
-  <si>
-    <t>CTX + Epirubicin</t>
   </si>
 </sst>
 </file>
@@ -477,12 +477,12 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4">
         <v>61.209999999999987</v>
@@ -491,12 +491,12 @@
         <v>52.642940645161282</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4">
         <v>52.75</v>
@@ -505,12 +505,12 @@
         <v>33.275815299999998</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4">
         <v>67.849999999999994</v>
@@ -519,12 +519,12 @@
         <v>51.999669246833321</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4">
         <v>46.266666666666673</v>
@@ -533,12 +533,12 @@
         <v>56.212154838709672</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <v>56.56</v>
@@ -547,12 +547,12 @@
         <v>47.621169999999999</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4">
         <v>67.25</v>
@@ -561,7 +561,7 @@
         <v>50.88900000000001</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -575,12 +575,12 @@
         <v>38.794008888888889</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4">
         <v>16.55</v>
@@ -589,12 +589,12 @@
         <v>45.338500666666668</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
         <v>53.666666666666657</v>
@@ -603,12 +603,12 @@
         <v>43.473419354838697</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4">
         <v>60.5</v>
@@ -617,12 +617,12 @@
         <v>53.258064516129018</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4">
         <v>74</v>
@@ -631,7 +631,7 @@
         <v>65.287275492903234</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,12 +645,12 @@
         <v>49.096428571428582</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <v>41.325000000000003</v>
@@ -659,12 +659,12 @@
         <v>49.555386470588239</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4">
         <v>55.31818181818182</v>
@@ -673,7 +673,7 @@
         <v>45.274541935483867</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
